--- a/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from emdn" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from SNOMED CT" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from SNOWMED CT" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>

--- a/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
@@ -8,7 +8,7 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from emdn" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from SNOWMED CT" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from SNOMED CT" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>

--- a/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20231215120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
@@ -82,7 +82,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
@@ -7,14 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from emdn" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from SNOMED CT" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from EMDN" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from EMDN 2" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20231215120000</t>
+    <t>20240726120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-07-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,16 +136,13 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://webgate.ec.europa.eu/dyna2/emdn</t>
+    <t>https://smt.esante.gouv.fr/terminologie-emdn</t>
   </si>
   <si>
     <t>8499008</t>
   </si>
   <si>
     <t>pouls</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -521,7 +518,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
@@ -8,13 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from EMDN" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from EMDN 2" r:id="rId5" sheetId="3"/>
+    <sheet name="Include from SNOMED CT" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>pouls</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -518,7 +521,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
+++ b/ig/main/ValueSet-JDV-J147-MethodHeartrate-ENS.xlsx
@@ -7,8 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from EMDN" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from SNOMED CT" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
